--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6675D134-DD69-464F-80CC-3EA49DC0FBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31352F2C-A666-4019-9CA5-77672E58548A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,94 +62,91 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>消耗GE</t>
+  </si>
+  <si>
+    <t>冷却CD执行的GE</t>
+  </si>
+  <si>
+    <t>冷却CD时长</t>
+  </si>
+  <si>
+    <t>描述标签</t>
+  </si>
+  <si>
+    <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>移动</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>ALMove</t>
+  </si>
+  <si>
+    <t>RunSpeedUp</t>
+  </si>
+  <si>
+    <t>加速</t>
+  </si>
+  <si>
+    <t>ALApplyEffect</t>
+  </si>
+  <si>
+    <t>1002;1001</t>
+  </si>
+  <si>
+    <t>debug_ge_ability</t>
+  </si>
+  <si>
+    <t>调试GE</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>debug_ge_2</t>
+  </si>
+  <si>
+    <t>调试ge2</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>玩家普通攻击</t>
+  </si>
+  <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>ALTimeline</t>
+  </si>
+  <si>
     <t>AbilityLogic</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>消耗GE</t>
-  </si>
-  <si>
-    <t>冷却CD执行的GE</t>
-  </si>
-  <si>
-    <t>冷却CD时长</t>
-  </si>
-  <si>
-    <t>描述标签</t>
-  </si>
-  <si>
-    <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
-  </si>
-  <si>
-    <t>move</t>
-  </si>
-  <si>
-    <t>移动</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>ALMove</t>
-  </si>
-  <si>
-    <t>RunSpeedUp</t>
-  </si>
-  <si>
-    <t>加速</t>
-  </si>
-  <si>
-    <t>ALApplyEffect</t>
-  </si>
-  <si>
-    <t>1002;1001</t>
-  </si>
-  <si>
-    <t>debug_ge_ability</t>
-  </si>
-  <si>
-    <t>调试GE</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>debug_ge_2</t>
-  </si>
-  <si>
-    <t>调试ge2</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>玩家普通攻击</t>
-  </si>
-  <si>
-    <t>3003</t>
-  </si>
-  <si>
-    <t>ALTimeline</t>
-  </si>
-  <si>
-    <t>AbilityLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -198,6 +195,10 @@
   </si>
   <si>
     <t>ActivationRequiredTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbilityLogicBase</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -352,13 +353,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -670,57 +671,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="M1" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="13"/>
+      <c r="N1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -762,50 +763,50 @@
       <c r="M2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="13"/>
+      <c r="N2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="14"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="N3" s="15" t="s">
         <v>13</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>14</v>
       </c>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
@@ -827,40 +828,40 @@
         <v>10001</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="O4" s="6">
         <v>0.5</v>
@@ -872,43 +873,43 @@
         <v>10002</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" s="7" t="s">
+      <c r="O5" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -916,43 +917,43 @@
         <v>1003</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -960,43 +961,43 @@
         <v>1005</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
@@ -1004,40 +1005,40 @@
         <v>20001</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="O8" s="2">
         <v>101</v>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,12 +28,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>id</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>CdEffect</t>
+  </si>
+  <si>
+    <t>Cd</t>
+  </si>
+  <si>
+    <t>AssetTags</t>
+  </si>
+  <si>
+    <t>CancelAbilityWithTags</t>
+  </si>
+  <si>
+    <t>BlockAbilityWithTags</t>
+  </si>
+  <si>
+    <t>ActivationOwnedTags</t>
+  </si>
+  <si>
+    <t>ActivationRequiredTags</t>
+  </si>
+  <si>
+    <t>ActivationBlockedTags</t>
+  </si>
+  <si>
+    <t>AbilityLogic</t>
   </si>
   <si>
     <t>##type</t>
@@ -45,10 +81,10 @@
     <t>string</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>(list#sep=;</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -59,12 +95,18 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbilityLogicBase</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -101,6 +143,9 @@
     <t>3001</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>ALMove</t>
   </si>
   <si>
@@ -144,69 +189,14 @@
   </si>
   <si>
     <t>ALTimeline</t>
-  </si>
-  <si>
-    <t>AbilityLogic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivationBlockedTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cost</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CdEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cd</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AssetTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CancelAbilityWithTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BlockAbilityWithTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivationOwnedTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivationRequiredTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AbilityLogicBase</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,14 +229,6 @@
       <color rgb="FF1F2328"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -334,47 +316,48 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -655,397 +638,397 @@
   <dimension ref="A1:AA8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="20" style="7" customWidth="1"/>
-    <col min="10" max="10" width="21.77734375" style="7" customWidth="1"/>
-    <col min="11" max="12" width="21" style="7" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="7" customWidth="1"/>
-    <col min="14" max="14" width="16.109375" style="6" customWidth="1"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1" style="8"/>
+    <col min="6" max="6" width="16.109375" customWidth="1" style="8"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1" style="8"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1" style="8"/>
+    <col min="9" max="9" width="20" customWidth="1" style="8"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1" style="8"/>
+    <col min="11" max="12" width="21" customWidth="1" style="8"/>
+    <col min="13" max="13" width="20.21875" customWidth="1" style="8"/>
+    <col min="14" max="14" width="16.109375" customWidth="1" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="1" ht="19.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="14"/>
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="15"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="14"/>
+        <v>15</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="15"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="17"/>
+        <v>25</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="18"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>14</v>
+      <c r="C4" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="6">
+        <v>30</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>20</v>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>16</v>
+        <v>36</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
+    <row r="6">
+      <c r="B6" s="6">
         <v>1003</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>26</v>
+      <c r="C6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+    <row r="7">
+      <c r="B7" s="5">
         <v>1005</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>29</v>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+    <row r="8">
+      <c r="B8" s="4">
         <v>20001</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" s="2">
+      <c r="C8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" s="3">
         <v>101</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="N1:AA1"/>
     <mergeCell ref="N2:AA2"/>
     <mergeCell ref="N3:AA3"/>
@@ -1053,5 +1036,6 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31352F2C-A666-4019-9CA5-77672E58548A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -95,7 +94,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="4" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>AbilityLogicBase</t>
@@ -189,12 +188,25 @@
   </si>
   <si>
     <t>ALTimeline</t>
+  </si>
+  <si>
+    <t>Dodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闪避
+</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>3002</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="0"/>
   <fonts count="5">
     <font>
@@ -316,11 +328,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
@@ -634,22 +647,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA8"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1" style="8"/>
-    <col min="6" max="6" width="16.109375" customWidth="1" style="8"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1" style="8"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1" style="8"/>
-    <col min="9" max="9" width="20" customWidth="1" style="8"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1" style="8"/>
-    <col min="11" max="12" width="21" customWidth="1" style="8"/>
-    <col min="13" max="13" width="20.21875" customWidth="1" style="8"/>
-    <col min="14" max="14" width="16.109375" customWidth="1" style="7"/>
+    <col min="4" max="5" width="15.375" customWidth="1" style="9"/>
+    <col min="6" max="6" width="16.125" customWidth="1" style="9"/>
+    <col min="7" max="7" width="15.375" customWidth="1" style="9"/>
+    <col min="8" max="8" width="23.625" customWidth="1" style="9"/>
+    <col min="9" max="9" width="20" customWidth="1" style="9"/>
+    <col min="10" max="10" width="21.75" customWidth="1" style="9"/>
+    <col min="11" max="12" width="21" customWidth="1" style="9"/>
+    <col min="13" max="13" width="20.25" customWidth="1" style="9"/>
+    <col min="14" max="14" width="16.125" customWidth="1" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2">
+    <row r="1" ht="17.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,40 +684,40 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="16"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -728,40 +741,40 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="16"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -785,32 +798,32 @@
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-      <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17"/>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Y3" s="18"/>
+      <c r="Z3" s="18"/>
+      <c r="AA3" s="19"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -825,28 +838,28 @@
       <c r="G4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="I4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="8" t="s">
+      <c r="L4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="8">
         <v>0.5</v>
       </c>
     </row>
@@ -855,176 +868,220 @@
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="E5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="8" t="s">
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="8" t="s">
+      <c r="M5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>1003</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="7" t="s">
+      <c r="E6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>1005</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="7" t="s">
+      <c r="E7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>20001</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="E8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="8" t="s">
+      <c r="L8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="4">
         <v>101</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3002</v>
+      </c>
+      <c r="F9" s="9">
+        <v>3001</v>
+      </c>
+      <c r="G9" s="9">
+        <v>120</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="3">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1090,7 @@
     <mergeCell ref="N2:AA2"/>
     <mergeCell ref="N3:AA3"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A822CA4-574A-45A5-B54C-60FB4269ECD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -80,10 +81,10 @@
     <t>string</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>(list#sep=;</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -94,7 +95,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="5" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>AbilityLogicBase</t>
@@ -140,9 +141,6 @@
   </si>
   <si>
     <t>3001</t>
-  </si>
-  <si>
-    <t>2010</t>
   </si>
   <si>
     <t>ALMove</t>
@@ -200,15 +198,31 @@
     <t>2006</t>
   </si>
   <si>
-    <t>3002</t>
+    <t>TagRequirementData?</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>3003;0;0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3001;0;0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010;0;0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3002;0;0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +255,14 @@
       <color rgb="FF1F2328"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -329,48 +351,50 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -647,22 +671,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.375" customWidth="1" style="9"/>
-    <col min="6" max="6" width="16.125" customWidth="1" style="9"/>
-    <col min="7" max="7" width="15.375" customWidth="1" style="9"/>
-    <col min="8" max="8" width="23.625" customWidth="1" style="9"/>
-    <col min="9" max="9" width="20" customWidth="1" style="9"/>
-    <col min="10" max="10" width="21.75" customWidth="1" style="9"/>
-    <col min="11" max="12" width="21" customWidth="1" style="9"/>
-    <col min="13" max="13" width="20.25" customWidth="1" style="9"/>
-    <col min="14" max="14" width="16.125" customWidth="1" style="8"/>
+    <col min="4" max="5" width="15.33203125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="20" style="8" customWidth="1"/>
+    <col min="10" max="10" width="21.77734375" style="8" customWidth="1"/>
+    <col min="11" max="12" width="21" style="8" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="8" customWidth="1"/>
+    <col min="14" max="14" width="16.109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25">
+    <row r="1" spans="1:27" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,42 +708,42 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="16"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="15"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -741,42 +765,42 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="14" t="s">
+      <c r="L2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="16"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="15"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -798,32 +822,32 @@
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="18"/>
-      <c r="AA3" s="19"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="18"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -838,254 +862,254 @@
       <c r="G4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="9" t="s">
+      <c r="I4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="9" t="s">
+      <c r="L4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="8">
+      <c r="O4" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="9" t="s">
+      <c r="O5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="D6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="B6" s="7">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" s="7" t="s">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="D7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="B7" s="6">
-        <v>1005</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="6" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>20001</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="D8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O8" s="3">
+        <v>101</v>
+      </c>
     </row>
-    <row r="8">
-      <c r="B8" s="5">
-        <v>20001</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="9" t="s">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
+        <v>5000</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3002</v>
+      </c>
+      <c r="F9" s="8">
+        <v>3001</v>
+      </c>
+      <c r="G9" s="8">
+        <v>120</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="8">
+        <v>3002</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="4">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="3">
-        <v>5000</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="9">
-        <v>3002</v>
-      </c>
-      <c r="F9" s="9">
-        <v>3001</v>
-      </c>
-      <c r="G9" s="9">
-        <v>120</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="2">
         <v>103</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="N1:AA1"/>
     <mergeCell ref="N2:AA2"/>
     <mergeCell ref="N3:AA3"/>
@@ -1093,6 +1117,5 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\EX_GAS_Config\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A822CA4-574A-45A5-B54C-60FB4269ECD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C431C59E-DDFD-44E7-8A19-C8278526F5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -210,11 +210,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>2010;0;0</t>
+    <t>0;0;3003</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>3002;0;0</t>
+    <t>0;0;2010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;0;3002</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -370,6 +374,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -387,9 +394,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -726,22 +730,22 @@
       <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="16"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -768,37 +772,37 @@
       <c r="H2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="13" t="s">
         <v>51</v>
       </c>
       <c r="K2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="16"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -825,22 +829,22 @@
       <c r="H3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-      <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17"/>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Y3" s="18"/>
+      <c r="Z3" s="18"/>
+      <c r="AA3" s="19"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -878,7 +882,7 @@
         <v>30</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>33</v>
@@ -1055,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>47</v>
@@ -1099,7 +1103,7 @@
         <v>30</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>47</v>
